--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_05_AI Product Thinking _ Requirements/Day_05_Phan_02_20_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_05_AI Product Thinking _ Requirements/Day_05_Phan_02_20_Cau.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
@@ -764,7 +764,7 @@
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người dùng cần biết làm gì khác ở mỗi trạng thái.</t>
+          <t>Hành vi phù hợp theo ba mức độ tin cậy đã hiệu chỉnh: Độ tin cậy cao: hiện kết quả và nguồn, người dùng có thể chấp nhận (a); Độ tin cậy trung bình: nói rõ chưa chắc chắn, hiện lựa chọn khác và yêu cầu người dùng kiểm tra (b); Độ tin cậy thấp: không tự thực hiện hành động, chuyển sang phương án dự phòng hoặc người xử lý (d).</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,4</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
@@ -877,7 +877,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Người kiểm tra phải tái tạo được AI đã sai gì và dữ liệu chỉnh sửa được dùng ở đâu.</t>
+          <t>Bản ghi tín hiệu chỉnh sửa đầy đủ cần: Mã giao dịch và đặc trưng đầu vào (a), Nhãn AI trước khi sửa (b), Nhãn người dùng chọn sau khi sửa (c), Mã sự kiện chỉnh sửa liên kết các bản ghi (d), và Nơi sử dụng dữ liệu để đánh giá/cải thiện (f).</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="G8" s="3" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>60</v>
@@ -926,7 +926,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Ba lỗi có thể quan trọng hơn mười lỗi nếu hậu quả khác nhau.</t>
+          <t>Trong 13 lỗi của bộ phân loại email, 3 email VIP bị phân loại nhầm vào Spam gây mất thương vụ có hậu quả nghiêm trọng hơn nhiều so với 10 email FYI vào Updates. Ưu tiên can thiệp đúng là nhóm VIP→Spam dựa trên mức độ nghiêm trọng của hậu quả.</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o4 → o5 → o1 → o3</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không phát hành thay đổi trước khi qua bước đánh giá.</t>
+          <t>Vòng phản hồi cải thiện hệ thống: Thu thập chỉnh sửa có dấu vết (o2) -&gt; Phân tích mẫu lỗi (o4) -&gt; Thay đổi prompt/dữ liệu/UX (o5) -&gt; Đánh giá thay đổi trên bộ kiểm thử cố định (o1) -&gt; Quan sát hành vi mới sau khi triển khai (o3).</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1085,7 +1085,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi dữ liệu từ sự kiện tới một thay đổi đã được kiểm chứng.</t>
+          <t>Ứng dụng có 1 triệu lượt dùng và ghi log mọi prompt nhưng không dùng được để cải thiện sản phẩm vì vòng phản hồi bị gãy ở khâu: Thiếu tín hiệu chẩn đoán liên quan (labeled feedback/error signal) và thiếu đường ống đưa dữ liệu vào quy trình cải thiện.</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,4</t>
         </is>
       </c>
       <c r="I12" s="4" t="n">
@@ -1140,7 +1140,7 @@
       <c r="J12" s="3" t="n"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dữ liệu phải trả lời được lỗi nào, thuộc phạm vi pháp lý/thời điểm nào và ai xác nhận.</t>
+          <t>Dữ liệu chất lượng cao để đánh giá và cải thiện trợ lý pháp lý Việt Nam: Văn bản pháp luật hiện hành có thời điểm ban hành và nguồn gốc rõ ràng (a), Các tình huống thực tế được luật sư gắn nhãn chuẩn (b), và Dữ liệu chỉnh sửa trước/sau từ chuyên gia kiểm tra (d).</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="G14" s="3" t="n"/>
       <c r="H14" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I14" s="4" t="n">
         <v>60</v>
@@ -1245,7 +1245,7 @@
       <c r="J14" s="3" t="n"/>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chi phí kiểm tra của con người là chi phí kỳ vọng: xác suất × chi phí khi xảy ra.</t>
+          <t>Chi phí biến đổi kỳ vọng cho mỗi kết quả = (3 lần gọi model × 0,02 USD) + (1 lần gọi tool × 0,01 USD) + (10% xác suất kiểm tra của con người × 0,50 USD) = 0,06 + 0,01 + 0,05 = 0,12 USD.</t>
         </is>
       </c>
     </row>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1403,7 +1403,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đánh dấu ba lớp can thiệp đã có: phát hiện, khôi phục, kiểm chứng. Tìm lớp còn trống.</t>
+          <t>Hệ thống phát hiện lỗi schema và chặn cứng nhưng HR không thể tiếp tục công việc, cho thấy hệ thống thiếu lớp can thiệp khôi phục (recovery intervention): Cần thêm cách khôi phục cho HR bằng cách cho phép nhập/sửa trường hoặc từ chối xử lý, đồng thời lưu dấu vết chỉnh sửa.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="G18" s="3" t="n"/>
       <c r="H18" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4" t="n">
         <v>60</v>
@@ -1452,7 +1452,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách điều được mô phỏng và quan sát khỏi hệ thống tự động ở phía sau chưa tồn tại.</t>
+          <t>Trong thử nghiệm Wizard-of-Oz, người vận hành thủ công tạo biên bản họp đạt 30/40; kết luận được hỗ trợ trực tiếp là quy trình làm việc và chất lượng đầu ra cho thấy giá trị với người dùng, nhưng chưa chứng minh mô hình tự động phía sau sẽ đạt chất lượng tương đương.</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="4" t="n">
         <v>60</v>
@@ -1500,7 +1500,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Bảng có thể chưa đủ luồng, nhưng mỗi trạng thái phải trung thực về điều đã quan sát.</t>
+          <t>Bản phân tích sản phẩm trung thực phải ghi nhận rõ ràng: Ghi 2 luồng đã trực tiếp quan sát kèm tài liệu đầu ra; đánh dấu luồng độ tin cậy thấp và việc chỉnh sửa là chưa quan sát được, đồng thời nêu rõ đầu vào/bằng chứng cần thử nghiệm thêm.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1555,7 +1555,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo luồng từ đầu vào thiếu đến hành động không thể đảo ngược; mỗi chỗ người dùng cần quyền quyết định phải có trạng thái rõ.</t>
+          <t>Để luồng gửi thư an toàn và đáp ứng quy ước: Thêm trạng thái hỏi hạn chót trước khi tạo bản nháp nếu thiếu dữ kiện (a), Thêm trạng thái cho phép người dùng xem lại, chỉnh sửa hoặc hủy bản nháp (b), và Thêm trạng thái bắt buộc xác nhận người nhận và nội dung trước khi thực thi gửi (c).</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="4" t="n">
         <v>60</v>
@@ -1661,7 +1661,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Viết riêng tổng lợi ích theo số kết quả được chấp nhận và tổng chi phí theo số yêu cầu.</t>
+          <t>Lợi ích ròng = Tổng lợi ích của các kết quả được chấp nhận − Tổng chi phí phát sinh trên toàn bộ yêu cầu: 1.000 × 0,40 × 3 − 1.000 × 0,50 = 1.200 − 500 = 700 USD.</t>
         </is>
       </c>
     </row>
